--- a/donation_forms/013_paypal_nonprofit_donation_form--donation_forms.xlsx
+++ b/donation_forms/013_paypal_nonprofit_donation_form--donation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How often?</t>
+          <t>Frequency Options</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Donation Status</t>
+          <t>Donation Status Options</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Email Confirmation</t>
+          <t>Email Confirmation Options</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Terms and Conditions</t>
+          <t>Terms And Conditions Options</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method Options</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Payment Status</t>
+          <t>Payment Status Label</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>terms_and_conditions_choices</t>
+          <t>email_confirmation_options_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>terms_and_conditions_options_choices</t>
+          <t>terms_and_conditions_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>terms_and_conditions_options_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>payment_method_options_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>payment_method_options_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
